--- a/Filtered_V3.0/COCUHA_HCA_Florida_University_Hospital.xlsx
+++ b/Filtered_V3.0/COCUHA_HCA_Florida_University_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advinity Healthcare (Ingenious Med)-Admissions </t>
+          <t>Advinity Healthcare (Ingenious Med)-ADMO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1915,7 +1915,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -1937,7 +1952,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1982,22 +1997,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AngelEye (NICU CameraSystem)-Admissions </t>
+          <t>AngelEye (NICU CameraSystem)-ADMO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ADMO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3078,6 +3078,21 @@
       <c r="P35" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -3099,7 +3114,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-Admissions </t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3144,22 +3159,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3181,7 +3196,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3226,22 +3241,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3616,22 +3616,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Scheduling </t>
+          <t>GE (CMI - Carescape Gateway)-CWSO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Admissions </t>
+          <t>GE (CPN - Gold Standard)-ADMO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Clinical Monitoring Results </t>
+          <t>GE (CPN - Gold Standard)-ITSHMRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCSCMI</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Monitoring Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-ITS HM Results </t>
+          <t>GE (CPN - Gold Standard)-LABRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Lab Results (Discrete) </t>
+          <t>GE (CPN - Gold Standard)-OMORDO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-OM Orders </t>
+          <t>GE (CPN - Gold Standard)-PCSCMI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4540,22 +4540,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>PCSCMI</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Clinical Monitoring Results </t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4685,6 +4685,21 @@
       <c r="P56" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4706,7 +4721,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4756,17 +4771,17 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4788,7 +4803,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4833,22 +4848,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4870,7 +4885,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4915,22 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5419,17 +5419,17 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6030,22 +6030,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6401,6 +6401,21 @@
       <c r="P79" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6422,7 +6437,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6472,17 +6487,17 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6519,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6554,17 +6569,17 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6601,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6636,7 +6651,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -6646,7 +6661,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6668,7 +6683,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6718,7 +6733,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -6728,7 +6743,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6750,7 +6765,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6800,17 +6815,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -6832,7 +6847,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6914,7 +6929,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6996,7 +7011,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7046,17 +7061,17 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7093,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7128,17 +7143,17 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7175,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7210,17 +7225,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7257,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7288,21 +7303,6 @@
       <c r="P90" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7432,6 +7432,21 @@
       <c r="P92" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7453,7 +7468,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7499,6 +7514,21 @@
       <c r="P93" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7550,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7570,17 +7600,17 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7602,7 +7632,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7652,17 +7682,17 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7714,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7766,7 +7796,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7816,7 +7846,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -7826,7 +7856,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7848,7 +7878,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7898,7 +7928,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -7908,7 +7938,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -7930,7 +7960,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8012,7 +8042,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8062,17 +8092,17 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -8094,7 +8124,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8144,17 +8174,17 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8206,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8258,7 +8288,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8308,17 +8338,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8370,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8422,7 +8452,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8472,17 +8502,17 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8534,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8554,17 +8584,17 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8616,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8636,17 +8666,17 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8698,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8718,17 +8748,17 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8780,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8800,17 +8830,17 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8862,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8878,21 +8908,6 @@
       <c r="P110" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8929,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8960,21 +8975,6 @@
       <c r="P111" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9520,7 +9520,22 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9542,7 +9557,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9609,7 +9624,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9654,22 +9669,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Care Management-Facility)-Admissions </t>
+          <t>HCA D&amp;IS (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9943,6 +9943,21 @@
       <c r="P125" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9964,7 +9979,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10014,17 +10029,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10046,7 +10061,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10096,17 +10111,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10143,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10178,7 +10193,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -10188,7 +10203,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10210,7 +10225,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10260,7 +10275,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10270,7 +10285,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -10292,7 +10307,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10342,7 +10357,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10352,7 +10367,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10374,7 +10389,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10424,17 +10439,17 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10471,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10506,17 +10521,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -10538,7 +10553,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10588,17 +10603,17 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10620,7 +10635,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10670,7 +10685,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -10680,7 +10695,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10717,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10752,17 +10767,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10799,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10830,21 +10845,6 @@
       <c r="P136" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>CWSO</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>SIU</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11458,6 +11458,21 @@
       <c r="P145" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -11479,7 +11494,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11529,17 +11544,17 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11576,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11611,17 +11626,17 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -11643,7 +11658,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11693,17 +11708,17 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11740,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11807,7 +11822,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11857,7 +11872,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -11867,7 +11882,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -11889,7 +11904,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11939,17 +11954,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -11971,7 +11986,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -12021,17 +12036,17 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -12053,7 +12068,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12103,17 +12118,17 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12150,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12190,12 +12205,12 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12232,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12267,17 +12282,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12299,7 +12314,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12381,7 +12396,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12431,17 +12446,17 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12478,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12513,17 +12528,17 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12560,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12595,17 +12610,17 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12642,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12677,17 +12692,17 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12724,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12755,21 +12770,6 @@
       <c r="P161" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom (Navacare Patient Flow)-Admissions </t>
+          <t>Hill-Rom (Navacare Patient Flow)-ADMO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15842,6 +15842,21 @@
       <c r="P202" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -15863,7 +15878,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15913,17 +15928,17 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -15945,7 +15960,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15995,7 +16010,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -16005,7 +16020,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16027,7 +16042,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16077,7 +16092,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -16087,7 +16102,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -16109,7 +16124,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16159,7 +16174,7 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -16169,7 +16184,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -16191,7 +16206,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -16273,7 +16288,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -16323,17 +16338,17 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -16355,7 +16370,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16405,17 +16420,17 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -16437,7 +16452,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople ED Patient Visit Data</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -16487,17 +16502,17 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16534,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Medication Administration</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16569,17 +16584,17 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16616,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16647,21 +16662,6 @@
       <c r="P212" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-Admissions </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ADMO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-ITS DI Results </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ITSDIRO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17957,7 +17957,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-ITS HM Results </t>
+          <t>Mednax (BabySteps Cloud)-ITSHMRO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Admissions </t>
+          <t>Net Health (ReDoc Xfit)-ADMO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Charges </t>
+          <t>Net Health (ReDoc Xfit)-ITSHMRO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19013,17 +19013,17 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-ITS HM Results </t>
+          <t>Net Health (ReDoc Xfit)-OMORDO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19090,22 +19090,22 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-OM Orders </t>
+          <t>Net Health (ReDoc Xfit)-Patient Accounting</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19172,22 +19172,22 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19816,6 +19816,21 @@
       <c r="P254" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19837,7 +19852,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19883,21 +19898,6 @@
       <c r="P255" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19981,7 +19981,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Admissions </t>
+          <t>Provation (Apex)-ADMO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-ITS HM Results </t>
+          <t>Provation (Apex)-CWSO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20237,22 +20237,22 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Scheduling </t>
+          <t>Provation (Apex)-ITSHMRO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20319,22 +20319,22 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE to MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-Admissions </t>
+          <t>Provation (MD - CMORE)-ADMO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE)-CWSO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20818,22 +20818,22 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -20855,7 +20855,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-Scheduling </t>
+          <t>Provation (MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20900,22 +20900,22 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sisco (FastPass)-Admissions </t>
+          <t>Sisco (FastPass)-ADMO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21143,7 +21143,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21307,7 +21307,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22298,7 +22298,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22781,6 +22781,21 @@
       <c r="P294" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -22802,7 +22817,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22852,17 +22867,17 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -22884,7 +22899,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -22966,7 +22981,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23048,7 +23063,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23130,7 +23145,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23180,17 +23195,17 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23227,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -23262,17 +23277,17 @@
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -23294,7 +23309,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23344,17 +23359,17 @@
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -23376,7 +23391,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23426,17 +23441,17 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23473,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -23504,21 +23519,6 @@
       <c r="P303" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q303" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R303" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
